--- a/backend/data/materials.xlsx
+++ b/backend/data/materials.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F2" t="n">
         <v>15</v>
@@ -1450,7 +1450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2330,6 +2330,58 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PURCHASE</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>T026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PURCHASE</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
